--- a/VerveStacks_NOR_grids_kan50/vt_vervestacks_NOR_v1.xlsx
+++ b/VerveStacks_NOR_grids_kan50/vt_vervestacks_NOR_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA3DCD53-33EE-4856-AB56-351F45AD202B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84075AD7-C566-4D13-BE32-8884C67491FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" xr2:uid="{74CFB458-94F5-4F02-B6E4-B4E39330D48E}"/>
+    <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" xr2:uid="{7CB39608-CBF4-4F39-B113-1A4DB217F742}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2243,7 +2243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADAA70D4-9EC1-497B-A876-735F6D0CD34C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59948AF4-300E-405F-B9EF-A4BA94A614A3}">
   <dimension ref="B9:Y10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2332,7 +2332,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE426AA-157E-49EE-86BD-695E354E7BB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62058486-52D3-4DA5-9D79-E87AEE2FA1D9}">
   <dimension ref="B9:Y88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7185,7 +7185,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF5399F-E876-4F16-8A58-8F7830CDC1BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF114FF-161C-4015-B055-BB5E7F549502}">
   <dimension ref="B9:Y408"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8004,7 +8004,7 @@
         <v>17</v>
       </c>
       <c r="U24" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="V24" t="s">
         <v>345</v>
@@ -8016,7 +8016,7 @@
         <v>347</v>
       </c>
       <c r="Y24" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
@@ -8054,7 +8054,7 @@
         <v>17</v>
       </c>
       <c r="U25" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="V25" t="s">
         <v>345</v>
@@ -8066,7 +8066,7 @@
         <v>347</v>
       </c>
       <c r="Y25" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
@@ -8754,7 +8754,7 @@
         <v>17</v>
       </c>
       <c r="U39" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="V39" t="s">
         <v>345</v>
@@ -8766,7 +8766,7 @@
         <v>347</v>
       </c>
       <c r="Y39" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.45">
@@ -8804,7 +8804,7 @@
         <v>17</v>
       </c>
       <c r="U40" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="V40" t="s">
         <v>345</v>
@@ -8816,7 +8816,7 @@
         <v>347</v>
       </c>
       <c r="Y40" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -9154,7 +9154,7 @@
         <v>17</v>
       </c>
       <c r="U47" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="V47" t="s">
         <v>345</v>
@@ -9166,7 +9166,7 @@
         <v>347</v>
       </c>
       <c r="Y47" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -9204,7 +9204,7 @@
         <v>17</v>
       </c>
       <c r="U48" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="V48" t="s">
         <v>345</v>
@@ -9216,7 +9216,7 @@
         <v>347</v>
       </c>
       <c r="Y48" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="49" spans="2:25" x14ac:dyDescent="0.45">
@@ -22855,7 +22855,7 @@
         <v>33</v>
       </c>
       <c r="P299">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="300" spans="2:16" x14ac:dyDescent="0.45">
@@ -22884,7 +22884,7 @@
         <v>32</v>
       </c>
       <c r="P300">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="301" spans="2:16" x14ac:dyDescent="0.45">
@@ -22913,7 +22913,7 @@
         <v>31</v>
       </c>
       <c r="P301">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="302" spans="2:16" x14ac:dyDescent="0.45">
@@ -22942,7 +22942,7 @@
         <v>33</v>
       </c>
       <c r="P302">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="303" spans="2:16" x14ac:dyDescent="0.45">
@@ -22971,7 +22971,7 @@
         <v>32</v>
       </c>
       <c r="P303">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="304" spans="2:16" x14ac:dyDescent="0.45">
@@ -23000,7 +23000,7 @@
         <v>31</v>
       </c>
       <c r="P304">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="305" spans="2:16" x14ac:dyDescent="0.45">
@@ -23029,7 +23029,7 @@
         <v>33</v>
       </c>
       <c r="P305">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="306" spans="2:16" x14ac:dyDescent="0.45">
@@ -23058,7 +23058,7 @@
         <v>32</v>
       </c>
       <c r="P306">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="307" spans="2:16" x14ac:dyDescent="0.45">
@@ -23087,7 +23087,7 @@
         <v>31</v>
       </c>
       <c r="P307">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="308" spans="2:16" x14ac:dyDescent="0.45">
@@ -23116,7 +23116,7 @@
         <v>33</v>
       </c>
       <c r="P308">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="309" spans="2:16" x14ac:dyDescent="0.45">
@@ -23145,7 +23145,7 @@
         <v>32</v>
       </c>
       <c r="P309">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="310" spans="2:16" x14ac:dyDescent="0.45">
@@ -23174,7 +23174,7 @@
         <v>31</v>
       </c>
       <c r="P310">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="311" spans="2:16" x14ac:dyDescent="0.45">
@@ -23203,7 +23203,7 @@
         <v>33</v>
       </c>
       <c r="P311">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="312" spans="2:16" x14ac:dyDescent="0.45">
@@ -23232,7 +23232,7 @@
         <v>32</v>
       </c>
       <c r="P312">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="313" spans="2:16" x14ac:dyDescent="0.45">
@@ -23261,7 +23261,7 @@
         <v>31</v>
       </c>
       <c r="P313">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="314" spans="2:16" x14ac:dyDescent="0.45">
@@ -23290,7 +23290,7 @@
         <v>33</v>
       </c>
       <c r="P314">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="315" spans="2:16" x14ac:dyDescent="0.45">
@@ -23319,7 +23319,7 @@
         <v>32</v>
       </c>
       <c r="P315">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="316" spans="2:16" x14ac:dyDescent="0.45">
@@ -23348,7 +23348,7 @@
         <v>31</v>
       </c>
       <c r="P316">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="317" spans="2:16" x14ac:dyDescent="0.45">
@@ -23377,7 +23377,7 @@
         <v>33</v>
       </c>
       <c r="P317">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="318" spans="2:16" x14ac:dyDescent="0.45">
@@ -23406,7 +23406,7 @@
         <v>32</v>
       </c>
       <c r="P318">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="319" spans="2:16" x14ac:dyDescent="0.45">
@@ -23435,7 +23435,7 @@
         <v>31</v>
       </c>
       <c r="P319">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="320" spans="2:16" x14ac:dyDescent="0.45">
@@ -23464,7 +23464,7 @@
         <v>33</v>
       </c>
       <c r="P320">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="321" spans="2:16" x14ac:dyDescent="0.45">
@@ -23493,7 +23493,7 @@
         <v>32</v>
       </c>
       <c r="P321">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="322" spans="2:16" x14ac:dyDescent="0.45">
@@ -23522,7 +23522,7 @@
         <v>31</v>
       </c>
       <c r="P322">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="323" spans="2:16" x14ac:dyDescent="0.45">
@@ -23551,7 +23551,7 @@
         <v>33</v>
       </c>
       <c r="P323">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="324" spans="2:16" x14ac:dyDescent="0.45">
@@ -23580,7 +23580,7 @@
         <v>32</v>
       </c>
       <c r="P324">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="325" spans="2:16" x14ac:dyDescent="0.45">
@@ -23609,7 +23609,7 @@
         <v>31</v>
       </c>
       <c r="P325">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="326" spans="2:16" x14ac:dyDescent="0.45">
@@ -23638,7 +23638,7 @@
         <v>33</v>
       </c>
       <c r="P326">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="327" spans="2:16" x14ac:dyDescent="0.45">
@@ -23667,7 +23667,7 @@
         <v>32</v>
       </c>
       <c r="P327">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="328" spans="2:16" x14ac:dyDescent="0.45">
@@ -23696,7 +23696,7 @@
         <v>31</v>
       </c>
       <c r="P328">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="329" spans="2:16" x14ac:dyDescent="0.45">
@@ -23725,7 +23725,7 @@
         <v>33</v>
       </c>
       <c r="P329">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="330" spans="2:16" x14ac:dyDescent="0.45">
@@ -23754,7 +23754,7 @@
         <v>32</v>
       </c>
       <c r="P330">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="331" spans="2:16" x14ac:dyDescent="0.45">
@@ -23783,7 +23783,7 @@
         <v>31</v>
       </c>
       <c r="P331">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="332" spans="2:16" x14ac:dyDescent="0.45">
@@ -23812,7 +23812,7 @@
         <v>33</v>
       </c>
       <c r="P332">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="333" spans="2:16" x14ac:dyDescent="0.45">
@@ -23841,7 +23841,7 @@
         <v>32</v>
       </c>
       <c r="P333">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="334" spans="2:16" x14ac:dyDescent="0.45">
@@ -23870,7 +23870,7 @@
         <v>31</v>
       </c>
       <c r="P334">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="335" spans="2:16" x14ac:dyDescent="0.45">
@@ -23899,7 +23899,7 @@
         <v>33</v>
       </c>
       <c r="P335">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="336" spans="2:16" x14ac:dyDescent="0.45">
@@ -23928,7 +23928,7 @@
         <v>32</v>
       </c>
       <c r="P336">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="337" spans="2:16" x14ac:dyDescent="0.45">
@@ -23957,7 +23957,7 @@
         <v>31</v>
       </c>
       <c r="P337">
-        <v>0.11917946072963187</v>
+        <v>0.11917946072963188</v>
       </c>
     </row>
     <row r="338" spans="2:16" x14ac:dyDescent="0.45">
@@ -26565,7 +26565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEED97B2-9E22-4696-9AEA-330951C8BD59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF75A4AF-65BE-40A7-B718-EC3B19466B6F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
